--- a/templates/barrisol_inv.xlsx
+++ b/templates/barrisol_inv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/barrisol-calculator/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB382564-6E04-FC44-94DE-17CD0B4B3EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCE7F73-0F18-CD4B-827C-F9E03F507637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
   <si>
     <t>Outward Inventory Sheet</t>
   </si>
@@ -718,13 +718,49 @@
   </si>
   <si>
     <t>DR-24240-BT-23</t>
+  </si>
+  <si>
+    <t>W-HINGE SCREW</t>
+  </si>
+  <si>
+    <t>AC-SC-WHNG</t>
+  </si>
+  <si>
+    <t>PVC CLIP B440/62</t>
+  </si>
+  <si>
+    <t>AC-GN-PC</t>
+  </si>
+  <si>
+    <t>RECTANGULAR TUBE 38x25</t>
+  </si>
+  <si>
+    <t>RT-3825-01</t>
+  </si>
+  <si>
+    <t>RECTANGULAR TUBE 50x25</t>
+  </si>
+  <si>
+    <t>RT-5025-02</t>
+  </si>
+  <si>
+    <t>ALUMINIUM SLAT 2MM</t>
+  </si>
+  <si>
+    <t>AC-GN-AS</t>
+  </si>
+  <si>
+    <t>ALLEN KEY</t>
+  </si>
+  <si>
+    <t>AC-GN-AK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -771,6 +807,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -792,7 +834,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -815,73 +857,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -895,43 +875,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,48 +1239,48 @@
   <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="37.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="4" customWidth="1"/>
-    <col min="5" max="6" width="19.1640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14" style="4" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="21.1640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="28" style="4" customWidth="1"/>
-    <col min="12" max="12" width="23.1640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="7" customWidth="1"/>
+    <col min="5" max="6" width="19.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14" style="7" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="21.1640625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="28" style="7" customWidth="1"/>
+    <col min="12" max="12" width="23.1640625" style="5" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12"/>
-      <c r="K1" s="13"/>
+      <c r="K1" s="12"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1350,855 +1320,855 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="7" t="str">
         <f>VLOOKUP(B4, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>BR-3501-PS-03</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="7">
         <v>3050</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="7">
         <f>ROUNDUP(D4*IF(H4="m", 0.05, IF(H4="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="7">
         <f>D4+E4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="7">
         <f>IF(ISBLANK(C4), F4,ROUND(((C4*F4)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="7" t="str">
         <f>VLOOKUP(B5, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>LT-1205-3K-10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="7">
         <f t="shared" ref="E5:E6" si="0">ROUNDUP(D5*IF(H5="m", 0.05, IF(H5="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="7">
         <f t="shared" ref="F5:F6" si="1">D5+E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="7">
         <f t="shared" ref="G5:G6" si="2">IF(ISBLANK(C5), F5,ROUND(((C5*F5)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="7" t="str">
         <f>VLOOKUP(B6, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>DR-12150-OF-12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="7" t="str">
         <f>VLOOKUP(B7, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-SW</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="7">
         <f>ROUNDUP(D7*IF(H7="m", 0.05, IF(H7="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="7">
         <f>D7+E7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="7">
         <f>IF(ISBLANK(C7), F7,ROUND(((C7*F7)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="7" t="str">
         <f>VLOOKUP(B8, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-SC-DW19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="7">
         <f t="shared" ref="E8:E58" si="3">ROUNDUP(D8*IF(H8="m", 0.05, IF(H8="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="7">
         <f t="shared" ref="F8:F58" si="4">D8+E8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="7">
         <f t="shared" ref="G8:G58" si="5">IF(ISBLANK(C8), F8,ROUND(((C8*F8)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="e">
+      <c r="A9" s="7" t="e">
         <f>VLOOKUP(B9, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="E9" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="7"/>
-      <c r="E10" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="B10" s="9"/>
+      <c r="E10" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="7"/>
-      <c r="E11" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="B11" s="9"/>
+      <c r="E11" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="7"/>
-      <c r="E12" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="B12" s="9"/>
+      <c r="E12" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="7"/>
-      <c r="E13" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="B13" s="9"/>
+      <c r="E13" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="7"/>
-      <c r="E14" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="B14" s="9"/>
+      <c r="E14" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="7"/>
-      <c r="E15" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="B15" s="9"/>
+      <c r="E15" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="7"/>
-      <c r="E16" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="B16" s="9"/>
+      <c r="E16" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="7"/>
-      <c r="E17" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="B17" s="9"/>
+      <c r="E17" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="7"/>
-      <c r="E18" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="B18" s="9"/>
+      <c r="E18" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="7"/>
-      <c r="E19" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="B19" s="9"/>
+      <c r="E19" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="7"/>
-      <c r="E20" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="B20" s="9"/>
+      <c r="E20" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="7"/>
-      <c r="E21" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="B21" s="9"/>
+      <c r="E21" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="7"/>
-      <c r="E22" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="B22" s="9"/>
+      <c r="E22" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="7"/>
-      <c r="E23" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="B23" s="9"/>
+      <c r="E23" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="7"/>
-      <c r="E24" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="B24" s="9"/>
+      <c r="E24" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="7"/>
-      <c r="E25" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="B25" s="9"/>
+      <c r="E25" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="7"/>
-      <c r="E26" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="B26" s="9"/>
+      <c r="E26" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="7"/>
-      <c r="E27" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="B27" s="9"/>
+      <c r="E27" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28" s="7"/>
-      <c r="E28" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="B28" s="9"/>
+      <c r="E28" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="7"/>
-      <c r="E29" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="B29" s="9"/>
+      <c r="E29" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="7"/>
-      <c r="E30" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="B30" s="9"/>
+      <c r="E30" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="7"/>
-      <c r="E31" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="B31" s="9"/>
+      <c r="E31" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="7"/>
-      <c r="E32" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="B32" s="9"/>
+      <c r="E32" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="7"/>
-      <c r="E33" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="B33" s="9"/>
+      <c r="E33" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B34" s="7"/>
-      <c r="E34" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="4">
+      <c r="B34" s="9"/>
+      <c r="E34" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="7"/>
-      <c r="E35" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="B35" s="9"/>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="7"/>
-      <c r="E36" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="4">
+      <c r="B36" s="9"/>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="7"/>
-      <c r="E37" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="4">
+      <c r="B37" s="9"/>
+      <c r="E37" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" s="7"/>
-      <c r="E38" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="B38" s="9"/>
+      <c r="E38" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B39" s="7"/>
-      <c r="E39" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="B39" s="9"/>
+      <c r="E39" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B40" s="7"/>
-      <c r="E40" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="4">
+      <c r="B40" s="9"/>
+      <c r="E40" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B41" s="7"/>
-      <c r="E41" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="4">
+      <c r="B41" s="9"/>
+      <c r="E41" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B42" s="7"/>
-      <c r="E42" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="4">
+      <c r="B42" s="9"/>
+      <c r="E42" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B43" s="7"/>
-      <c r="E43" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="4">
+      <c r="B43" s="9"/>
+      <c r="E43" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="7"/>
-      <c r="E44" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="4">
+      <c r="B44" s="9"/>
+      <c r="E44" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="7"/>
-      <c r="E45" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="4">
+      <c r="B45" s="9"/>
+      <c r="E45" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="7"/>
-      <c r="E46" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="4">
+      <c r="B46" s="9"/>
+      <c r="E46" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B47" s="7"/>
-      <c r="E47" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="B47" s="9"/>
+      <c r="E47" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B48" s="7"/>
-      <c r="E48" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
+      <c r="B48" s="9"/>
+      <c r="E48" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E49" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="E49" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E50" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="E50" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E51" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="4">
+      <c r="E51" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E52" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="4">
+      <c r="E52" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E53" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="E53" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E54" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="4">
+      <c r="E54" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E55" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="E55" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E56" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="4">
+      <c r="E56" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E57" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="4">
+      <c r="E57" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E58" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="4">
+      <c r="E58" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2216,31 +2186,31 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{08048798-6795-C449-9AE7-C899D2E782E1}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$67:$A$90</xm:f>
+            <xm:f>ACCESSORIES!$A$74:$A$97</xm:f>
           </x14:formula1>
           <xm:sqref>B5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4997BC04-D872-224A-BF31-FD022CCCA4C3}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$91:$A$109</xm:f>
+            <xm:f>ACCESSORIES!$A$110:$A$116</xm:f>
           </x14:formula1>
           <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262F6D70-A5C9-F142-91D0-A15EA0B7D977}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$49:$A$66</xm:f>
+            <xm:f>ACCESSORIES!$A$56:$A$73</xm:f>
           </x14:formula1>
           <xm:sqref>B4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{99A4488E-8CF0-C949-9642-E2CA61A2C666}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$47:$A$48</xm:f>
+            <xm:f>ACCESSORIES!$A$26:$A$27</xm:f>
           </x14:formula1>
           <xm:sqref>B7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17EE753A-A9AE-2A49-8653-B215D3CE9822}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$20:$A$23</xm:f>
+            <xm:f>ACCESSORIES!$A$36:$A$39</xm:f>
           </x14:formula1>
           <xm:sqref>B8</xm:sqref>
         </x14:dataValidation>
@@ -2258,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED1BDD3-06DA-CA42-BD86-FA2419A38AFC}">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="1"/>
@@ -2266,874 +2236,930 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B38" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B44" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B45" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B46" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B47" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B48" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B49" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B50" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B51" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B57" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B58" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B59" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B61" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B62" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B63" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B64" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B65" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B66" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="8" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B67" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B68" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B69" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B70" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B71" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B72" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="8" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B73" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B74" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B75" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B76" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="8" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B77" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B78" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B79" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="8" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B80" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="8" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B81" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="8" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B82" s="6" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="8" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B83" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="8" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B84" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="8" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B85" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="8" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B86" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B87" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="8" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B88" s="6" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="8" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B89" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="8" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B90" s="6" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="8" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B91" s="6" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="8" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B92" s="6" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="8" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B93" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="8" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B94" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="8" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B95" s="6" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="8" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B96" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="8" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B97" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="8" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B98" s="6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="8" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B99" s="6" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="8" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B100" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="8" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B101" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="8" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B102" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="8" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B103" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="8" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B104" s="6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="8" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B105" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="8" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B106" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="8" t="s">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B107" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="8" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B108" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="8" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B109" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="8" t="s">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B110" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="8" t="s">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B111" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="8" t="s">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B112" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="8" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B113" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="8" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B114" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="8" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B115" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="8" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B116" s="6" t="s">
         <v>226</v>
       </c>
     </row>

--- a/templates/barrisol_inv.xlsx
+++ b/templates/barrisol_inv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/barrisol-calculator/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCE7F73-0F18-CD4B-827C-F9E03F507637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2980FADC-2D54-B440-9C7D-2378E7405AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -888,6 +888,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -900,8 +902,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1254,33 +1254,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -2192,7 +2192,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4997BC04-D872-224A-BF31-FD022CCCA4C3}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$110:$A$116</xm:f>
+            <xm:f>ACCESSORIES!$A$98:$A$116</xm:f>
           </x14:formula1>
           <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
@@ -2452,7 +2452,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="11" t="s">
         <v>231</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -2460,7 +2460,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -2660,7 +2660,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="10" t="s">
         <v>235</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -2668,7 +2668,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="10" t="s">
         <v>237</v>
       </c>
       <c r="B55" s="6" t="s">
